--- a/data/extracted/inventory-receipts/CONTENEDOR FRIA 200 26 MARZO.xlsx
+++ b/data/extracted/inventory-receipts/CONTENEDOR FRIA 200 26 MARZO.xlsx
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2C5C7E-3542-4324-B828-3B0011212072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="9465"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -3950,7 +3963,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -3991,12 +4004,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4276,50 +4288,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L1086"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -4357,12 +4369,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -4400,7 +4412,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -4438,7 +4450,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -4476,7 +4488,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -4514,7 +4526,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -4552,7 +4564,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -4590,7 +4602,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -4628,7 +4640,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -4666,7 +4678,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -4704,7 +4716,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -4742,7 +4754,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -4780,7 +4792,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -4818,7 +4830,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -4856,7 +4868,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -4894,7 +4906,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -4932,7 +4944,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -4970,7 +4982,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -5008,7 +5020,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -5046,7 +5058,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -5084,7 +5096,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -5122,7 +5134,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -5160,7 +5172,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -5198,7 +5210,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -5236,7 +5248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
@@ -5274,7 +5286,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -5312,7 +5324,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -5350,7 +5362,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -5388,7 +5400,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -5426,7 +5438,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -5464,7 +5476,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -5502,7 +5514,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -5540,7 +5552,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -5578,7 +5590,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -5616,7 +5628,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -5654,7 +5666,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
@@ -5692,7 +5704,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -5730,7 +5742,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -5768,7 +5780,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -5806,7 +5818,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -5844,7 +5856,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -5882,7 +5894,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -5920,7 +5932,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -5958,7 +5970,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
@@ -5996,7 +6008,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
@@ -6034,7 +6046,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -6072,7 +6084,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -6110,7 +6122,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -6148,7 +6160,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
@@ -6186,7 +6198,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
@@ -6224,7 +6236,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -6262,7 +6274,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -6300,7 +6312,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -6338,7 +6350,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>19</v>
       </c>
@@ -6376,7 +6388,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -6414,7 +6426,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -6452,7 +6464,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -6490,7 +6502,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>19</v>
       </c>
@@ -6528,7 +6540,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6566,7 +6578,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>19</v>
       </c>
@@ -6604,7 +6616,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>19</v>
       </c>
@@ -6642,7 +6654,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>19</v>
       </c>
@@ -6680,7 +6692,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>19</v>
       </c>
@@ -6718,7 +6730,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -6756,7 +6768,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>19</v>
       </c>
@@ -6794,7 +6806,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -6832,7 +6844,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>19</v>
       </c>
@@ -6870,7 +6882,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -6908,7 +6920,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>19</v>
       </c>
@@ -6946,7 +6958,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>19</v>
       </c>
@@ -6984,7 +6996,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>19</v>
       </c>
@@ -7022,7 +7034,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -7060,7 +7072,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>19</v>
       </c>
@@ -7098,7 +7110,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>19</v>
       </c>
@@ -7136,7 +7148,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>19</v>
       </c>
@@ -7174,7 +7186,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
@@ -7212,7 +7224,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>19</v>
       </c>
@@ -7250,7 +7262,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -7288,7 +7300,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>19</v>
       </c>
@@ -7326,7 +7338,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>19</v>
       </c>
@@ -7364,7 +7376,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>19</v>
       </c>
@@ -7402,7 +7414,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>19</v>
       </c>
@@ -7440,7 +7452,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>19</v>
       </c>
@@ -7478,7 +7490,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -7516,7 +7528,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>19</v>
       </c>
@@ -7554,7 +7566,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>19</v>
       </c>
@@ -7592,7 +7604,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
@@ -7630,7 +7642,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>19</v>
       </c>
@@ -7668,7 +7680,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>19</v>
       </c>
@@ -7706,7 +7718,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>19</v>
       </c>
@@ -7744,7 +7756,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>19</v>
       </c>
@@ -7782,7 +7794,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>19</v>
       </c>
@@ -7820,7 +7832,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>19</v>
       </c>
@@ -7858,7 +7870,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>19</v>
       </c>
@@ -7896,7 +7908,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>19</v>
       </c>
@@ -7934,7 +7946,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F101" s="1" t="s">
         <v>226</v>
       </c>
@@ -7954,7 +7966,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F102" s="1" t="s">
         <v>224</v>
       </c>
@@ -7971,7 +7983,7 @@
         <v>1941.2000000000003</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>19</v>
       </c>
@@ -8009,7 +8021,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>19</v>
       </c>
@@ -8047,7 +8059,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>19</v>
       </c>
@@ -8085,7 +8097,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>19</v>
       </c>
@@ -8123,7 +8135,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>19</v>
       </c>
@@ -8161,7 +8173,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>19</v>
       </c>
@@ -8199,7 +8211,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>19</v>
       </c>
@@ -8237,7 +8249,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>19</v>
       </c>
@@ -8275,7 +8287,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>19</v>
       </c>
@@ -8313,7 +8325,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>19</v>
       </c>
@@ -8351,7 +8363,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>19</v>
       </c>
@@ -8389,7 +8401,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>19</v>
       </c>
@@ -8427,7 +8439,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>19</v>
       </c>
@@ -8465,7 +8477,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>19</v>
       </c>
@@ -8503,7 +8515,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>19</v>
       </c>
@@ -8541,7 +8553,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>19</v>
       </c>
@@ -8579,7 +8591,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>19</v>
       </c>
@@ -8617,7 +8629,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>19</v>
       </c>
@@ -8655,7 +8667,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>19</v>
       </c>
@@ -8693,7 +8705,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>19</v>
       </c>
@@ -8731,7 +8743,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>19</v>
       </c>
@@ -8769,7 +8781,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>19</v>
       </c>
@@ -8807,7 +8819,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>19</v>
       </c>
@@ -8845,7 +8857,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>19</v>
       </c>
@@ -8883,7 +8895,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>19</v>
       </c>
@@ -8921,7 +8933,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>19</v>
       </c>
@@ -8959,7 +8971,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>19</v>
       </c>
@@ -8997,7 +9009,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>19</v>
       </c>
@@ -9035,7 +9047,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>19</v>
       </c>
@@ -9073,7 +9085,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>19</v>
       </c>
@@ -9111,7 +9123,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>19</v>
       </c>
@@ -9149,7 +9161,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>19</v>
       </c>
@@ -9187,7 +9199,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>19</v>
       </c>
@@ -9225,7 +9237,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>19</v>
       </c>
@@ -9263,7 +9275,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>19</v>
       </c>
@@ -9301,7 +9313,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>19</v>
       </c>
@@ -9339,7 +9351,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>19</v>
       </c>
@@ -9377,7 +9389,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>19</v>
       </c>
@@ -9415,7 +9427,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>19</v>
       </c>
@@ -9453,7 +9465,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>19</v>
       </c>
@@ -9491,7 +9503,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>19</v>
       </c>
@@ -9529,7 +9541,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>19</v>
       </c>
@@ -9567,7 +9579,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>19</v>
       </c>
@@ -9605,7 +9617,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>19</v>
       </c>
@@ -9643,7 +9655,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>19</v>
       </c>
@@ -9681,7 +9693,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>19</v>
       </c>
@@ -9719,7 +9731,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>19</v>
       </c>
@@ -9757,7 +9769,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>19</v>
       </c>
@@ -9795,7 +9807,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>19</v>
       </c>
@@ -9833,7 +9845,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>19</v>
       </c>
@@ -9871,7 +9883,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>19</v>
       </c>
@@ -9909,7 +9921,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>19</v>
       </c>
@@ -9947,7 +9959,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>19</v>
       </c>
@@ -9985,7 +9997,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>19</v>
       </c>
@@ -10023,7 +10035,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>19</v>
       </c>
@@ -10061,7 +10073,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>19</v>
       </c>
@@ -10099,7 +10111,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>19</v>
       </c>
@@ -10137,7 +10149,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>19</v>
       </c>
@@ -10175,7 +10187,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>19</v>
       </c>
@@ -10213,7 +10225,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>19</v>
       </c>
@@ -10251,7 +10263,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>19</v>
       </c>
@@ -10289,7 +10301,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>19</v>
       </c>
@@ -10327,7 +10339,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>19</v>
       </c>
@@ -10365,7 +10377,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>19</v>
       </c>
@@ -10403,7 +10415,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>19</v>
       </c>
@@ -10441,7 +10453,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>19</v>
       </c>
@@ -10479,7 +10491,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>19</v>
       </c>
@@ -10517,7 +10529,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>19</v>
       </c>
@@ -10555,7 +10567,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>19</v>
       </c>
@@ -10593,7 +10605,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>19</v>
       </c>
@@ -10631,7 +10643,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>19</v>
       </c>
@@ -10669,7 +10681,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>19</v>
       </c>
@@ -10707,7 +10719,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>19</v>
       </c>
@@ -10745,7 +10757,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>19</v>
       </c>
@@ -10783,7 +10795,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>19</v>
       </c>
@@ -10821,7 +10833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>19</v>
       </c>
@@ -10859,7 +10871,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>19</v>
       </c>
@@ -10897,7 +10909,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>19</v>
       </c>
@@ -10935,7 +10947,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>19</v>
       </c>
@@ -10973,7 +10985,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>19</v>
       </c>
@@ -11011,7 +11023,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>19</v>
       </c>
@@ -11049,7 +11061,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>19</v>
       </c>
@@ -11087,7 +11099,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>19</v>
       </c>
@@ -11125,7 +11137,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>19</v>
       </c>
@@ -11163,7 +11175,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>19</v>
       </c>
@@ -11201,7 +11213,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>19</v>
       </c>
@@ -11239,7 +11251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>19</v>
       </c>
@@ -11277,7 +11289,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>19</v>
       </c>
@@ -11315,7 +11327,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>19</v>
       </c>
@@ -11353,7 +11365,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>19</v>
       </c>
@@ -11391,7 +11403,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>19</v>
       </c>
@@ -11429,7 +11441,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>19</v>
       </c>
@@ -11467,7 +11479,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>19</v>
       </c>
@@ -11505,7 +11517,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>19</v>
       </c>
@@ -11543,7 +11555,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>19</v>
       </c>
@@ -11581,7 +11593,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>19</v>
       </c>
@@ -11619,7 +11631,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>19</v>
       </c>
@@ -11657,7 +11669,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>19</v>
       </c>
@@ -11695,7 +11707,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>19</v>
       </c>
@@ -11733,7 +11745,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>19</v>
       </c>
@@ -11771,7 +11783,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>19</v>
       </c>
@@ -11809,7 +11821,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>19</v>
       </c>
@@ -11847,7 +11859,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>19</v>
       </c>
@@ -11885,7 +11897,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>19</v>
       </c>
@@ -11923,7 +11935,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>19</v>
       </c>
@@ -11961,7 +11973,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>19</v>
       </c>
@@ -11999,7 +12011,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>19</v>
       </c>
@@ -12037,7 +12049,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>19</v>
       </c>
@@ -12075,7 +12087,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>19</v>
       </c>
@@ -12113,7 +12125,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>19</v>
       </c>
@@ -12151,7 +12163,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>19</v>
       </c>
@@ -12189,7 +12201,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>19</v>
       </c>
@@ -12227,7 +12239,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>19</v>
       </c>
@@ -12265,7 +12277,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>19</v>
       </c>
@@ -12303,7 +12315,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>19</v>
       </c>
@@ -12341,7 +12353,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>19</v>
       </c>
@@ -12379,7 +12391,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>19</v>
       </c>
@@ -12417,7 +12429,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>19</v>
       </c>
@@ -12455,7 +12467,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>19</v>
       </c>
@@ -12493,7 +12505,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>19</v>
       </c>
@@ -12531,7 +12543,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>19</v>
       </c>
@@ -12569,7 +12581,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>19</v>
       </c>
@@ -12607,7 +12619,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>19</v>
       </c>
@@ -12645,7 +12657,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>19</v>
       </c>
@@ -12683,7 +12695,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>19</v>
       </c>
@@ -12721,7 +12733,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>19</v>
       </c>
@@ -12759,7 +12771,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>19</v>
       </c>
@@ -12797,7 +12809,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>19</v>
       </c>
@@ -12835,7 +12847,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>19</v>
       </c>
@@ -12873,7 +12885,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>19</v>
       </c>
@@ -12911,7 +12923,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>19</v>
       </c>
@@ -12949,7 +12961,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>19</v>
       </c>
@@ -12987,7 +12999,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>19</v>
       </c>
@@ -13025,7 +13037,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>19</v>
       </c>
@@ -13063,7 +13075,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>19</v>
       </c>
@@ -13101,7 +13113,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>19</v>
       </c>
@@ -13139,7 +13151,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>19</v>
       </c>
@@ -13177,7 +13189,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>19</v>
       </c>
@@ -13215,7 +13227,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>19</v>
       </c>
@@ -13253,7 +13265,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>19</v>
       </c>
@@ -13291,7 +13303,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>19</v>
       </c>
@@ -13329,7 +13341,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>19</v>
       </c>
@@ -13367,7 +13379,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>19</v>
       </c>
@@ -13405,7 +13417,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>19</v>
       </c>
@@ -13443,7 +13455,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>19</v>
       </c>
@@ -13481,7 +13493,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>19</v>
       </c>
@@ -13519,7 +13531,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>19</v>
       </c>
@@ -13557,7 +13569,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>19</v>
       </c>
@@ -13595,7 +13607,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>19</v>
       </c>
@@ -13633,7 +13645,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>19</v>
       </c>
@@ -13671,7 +13683,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>19</v>
       </c>
@@ -13709,7 +13721,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>19</v>
       </c>
@@ -13747,7 +13759,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>19</v>
       </c>
@@ -13785,7 +13797,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>19</v>
       </c>
@@ -13823,7 +13835,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>19</v>
       </c>
@@ -13861,7 +13873,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>19</v>
       </c>
@@ -13899,7 +13911,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F259" s="1" t="s">
         <v>226</v>
       </c>
@@ -13919,7 +13931,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F260" s="1" t="s">
         <v>264</v>
       </c>
@@ -13936,7 +13948,7 @@
         <v>3211.5999999999995</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>19</v>
       </c>
@@ -13974,7 +13986,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>19</v>
       </c>
@@ -14012,7 +14024,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>19</v>
       </c>
@@ -14050,7 +14062,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>19</v>
       </c>
@@ -14088,7 +14100,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>19</v>
       </c>
@@ -14126,7 +14138,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>19</v>
       </c>
@@ -14164,7 +14176,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>19</v>
       </c>
@@ -14202,7 +14214,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>19</v>
       </c>
@@ -14240,7 +14252,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>19</v>
       </c>
@@ -14278,7 +14290,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>19</v>
       </c>
@@ -14316,7 +14328,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>19</v>
       </c>
@@ -14354,7 +14366,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>19</v>
       </c>
@@ -14392,7 +14404,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>19</v>
       </c>
@@ -14430,7 +14442,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>19</v>
       </c>
@@ -14468,7 +14480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>19</v>
       </c>
@@ -14506,7 +14518,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>19</v>
       </c>
@@ -14544,7 +14556,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>19</v>
       </c>
@@ -14582,7 +14594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>19</v>
       </c>
@@ -14620,7 +14632,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>19</v>
       </c>
@@ -14658,7 +14670,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>19</v>
       </c>
@@ -14696,7 +14708,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>19</v>
       </c>
@@ -14734,7 +14746,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>19</v>
       </c>
@@ -14772,7 +14784,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>19</v>
       </c>
@@ -14810,7 +14822,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>19</v>
       </c>
@@ -14848,7 +14860,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>19</v>
       </c>
@@ -14886,7 +14898,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>19</v>
       </c>
@@ -14924,7 +14936,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>19</v>
       </c>
@@ -14962,7 +14974,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>19</v>
       </c>
@@ -15000,7 +15012,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>19</v>
       </c>
@@ -15038,7 +15050,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>19</v>
       </c>
@@ -15076,7 +15088,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>19</v>
       </c>
@@ -15114,7 +15126,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>19</v>
       </c>
@@ -15152,7 +15164,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>19</v>
       </c>
@@ -15190,7 +15202,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>19</v>
       </c>
@@ -15228,7 +15240,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>19</v>
       </c>
@@ -15266,7 +15278,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>19</v>
       </c>
@@ -15304,7 +15316,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>19</v>
       </c>
@@ -15342,7 +15354,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>19</v>
       </c>
@@ -15380,7 +15392,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>19</v>
       </c>
@@ -15418,7 +15430,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>19</v>
       </c>
@@ -15456,7 +15468,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>19</v>
       </c>
@@ -15494,7 +15506,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>19</v>
       </c>
@@ -15532,7 +15544,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>19</v>
       </c>
@@ -15570,7 +15582,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>19</v>
       </c>
@@ -15608,7 +15620,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>19</v>
       </c>
@@ -15646,7 +15658,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>19</v>
       </c>
@@ -15684,7 +15696,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>19</v>
       </c>
@@ -15722,7 +15734,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>19</v>
       </c>
@@ -15760,7 +15772,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>19</v>
       </c>
@@ -15798,7 +15810,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>19</v>
       </c>
@@ -15836,7 +15848,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>19</v>
       </c>
@@ -15874,7 +15886,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>19</v>
       </c>
@@ -15912,7 +15924,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>19</v>
       </c>
@@ -15950,7 +15962,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>19</v>
       </c>
@@ -15988,7 +16000,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>19</v>
       </c>
@@ -16026,7 +16038,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>19</v>
       </c>
@@ -16064,7 +16076,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>19</v>
       </c>
@@ -16102,7 +16114,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>19</v>
       </c>
@@ -16140,7 +16152,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>19</v>
       </c>
@@ -16178,7 +16190,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>19</v>
       </c>
@@ -16216,7 +16228,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>19</v>
       </c>
@@ -16254,7 +16266,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>19</v>
       </c>
@@ -16292,7 +16304,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>19</v>
       </c>
@@ -16330,7 +16342,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>19</v>
       </c>
@@ -16368,7 +16380,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>19</v>
       </c>
@@ -16406,7 +16418,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>19</v>
       </c>
@@ -16444,7 +16456,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>19</v>
       </c>
@@ -16482,7 +16494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>19</v>
       </c>
@@ -16520,7 +16532,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>19</v>
       </c>
@@ -16558,7 +16570,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>19</v>
       </c>
@@ -16596,7 +16608,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>19</v>
       </c>
@@ -16634,7 +16646,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>19</v>
       </c>
@@ -16672,7 +16684,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>19</v>
       </c>
@@ -16710,7 +16722,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>19</v>
       </c>
@@ -16748,7 +16760,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>19</v>
       </c>
@@ -16786,7 +16798,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>19</v>
       </c>
@@ -16824,7 +16836,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>19</v>
       </c>
@@ -16862,7 +16874,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>19</v>
       </c>
@@ -16900,7 +16912,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>19</v>
       </c>
@@ -16938,7 +16950,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>19</v>
       </c>
@@ -16976,7 +16988,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>19</v>
       </c>
@@ -17014,7 +17026,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>19</v>
       </c>
@@ -17052,7 +17064,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>19</v>
       </c>
@@ -17090,7 +17102,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>19</v>
       </c>
@@ -17128,7 +17140,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>19</v>
       </c>
@@ -17166,7 +17178,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>19</v>
       </c>
@@ -17204,7 +17216,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>19</v>
       </c>
@@ -17242,7 +17254,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>19</v>
       </c>
@@ -17280,7 +17292,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>19</v>
       </c>
@@ -17318,7 +17330,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F350" s="1" t="s">
         <v>226</v>
       </c>
@@ -17338,7 +17350,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F351" s="1" t="s">
         <v>214</v>
       </c>
@@ -17355,7 +17367,7 @@
         <v>1870.3999999999999</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>19</v>
       </c>
@@ -17393,7 +17405,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>19</v>
       </c>
@@ -17431,7 +17443,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>19</v>
       </c>
@@ -17469,7 +17481,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>19</v>
       </c>
@@ -17507,7 +17519,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>19</v>
       </c>
@@ -17545,7 +17557,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>19</v>
       </c>
@@ -17583,7 +17595,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>19</v>
       </c>
@@ -17621,7 +17633,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>19</v>
       </c>
@@ -17659,7 +17671,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>19</v>
       </c>
@@ -17697,7 +17709,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>19</v>
       </c>
@@ -17735,7 +17747,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>19</v>
       </c>
@@ -17773,7 +17785,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>19</v>
       </c>
@@ -17811,7 +17823,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>19</v>
       </c>
@@ -17849,7 +17861,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>19</v>
       </c>
@@ -17887,7 +17899,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>19</v>
       </c>
@@ -17925,7 +17937,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>19</v>
       </c>
@@ -17963,7 +17975,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>19</v>
       </c>
@@ -18001,7 +18013,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>19</v>
       </c>
@@ -18039,7 +18051,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>19</v>
       </c>
@@ -18077,7 +18089,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>19</v>
       </c>
@@ -18115,7 +18127,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>19</v>
       </c>
@@ -18153,7 +18165,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>19</v>
       </c>
@@ -18191,7 +18203,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>19</v>
       </c>
@@ -18229,7 +18241,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>19</v>
       </c>
@@ -18267,7 +18279,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>19</v>
       </c>
@@ -18305,7 +18317,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>19</v>
       </c>
@@ -18343,7 +18355,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>19</v>
       </c>
@@ -18381,7 +18393,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>19</v>
       </c>
@@ -18419,7 +18431,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
         <v>19</v>
       </c>
@@ -18457,7 +18469,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
         <v>19</v>
       </c>
@@ -18495,7 +18507,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>19</v>
       </c>
@@ -18533,7 +18545,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>19</v>
       </c>
@@ -18571,7 +18583,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>19</v>
       </c>
@@ -18609,7 +18621,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>19</v>
       </c>
@@ -18647,7 +18659,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>19</v>
       </c>
@@ -18685,7 +18697,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>19</v>
       </c>
@@ -18723,7 +18735,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>19</v>
       </c>
@@ -18761,7 +18773,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>19</v>
       </c>
@@ -18799,7 +18811,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>19</v>
       </c>
@@ -18837,7 +18849,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>19</v>
       </c>
@@ -18875,7 +18887,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>19</v>
       </c>
@@ -18913,7 +18925,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>19</v>
       </c>
@@ -18951,7 +18963,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>19</v>
       </c>
@@ -18989,7 +19001,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>19</v>
       </c>
@@ -19027,7 +19039,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>19</v>
       </c>
@@ -19065,7 +19077,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F397" s="1" t="s">
         <v>226</v>
       </c>
@@ -19085,7 +19097,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F398" s="1" t="s">
         <v>579</v>
       </c>
@@ -19105,7 +19117,7 @@
         <v>949.2</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>19</v>
       </c>
@@ -19143,7 +19155,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>19</v>
       </c>
@@ -19181,7 +19193,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>19</v>
       </c>
@@ -19219,7 +19231,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>19</v>
       </c>
@@ -19257,7 +19269,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
         <v>19</v>
       </c>
@@ -19295,7 +19307,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
         <v>19</v>
       </c>
@@ -19333,7 +19345,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
         <v>19</v>
       </c>
@@ -19371,7 +19383,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
         <v>19</v>
       </c>
@@ -19409,7 +19421,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
         <v>19</v>
       </c>
@@ -19447,7 +19459,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
         <v>19</v>
       </c>
@@ -19485,7 +19497,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
         <v>19</v>
       </c>
@@ -19523,7 +19535,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
         <v>19</v>
       </c>
@@ -19561,7 +19573,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
         <v>19</v>
       </c>
@@ -19599,7 +19611,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>19</v>
       </c>
@@ -19637,7 +19649,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>19</v>
       </c>
@@ -19675,7 +19687,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
         <v>19</v>
       </c>
@@ -19713,7 +19725,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
         <v>19</v>
       </c>
@@ -19751,7 +19763,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
         <v>19</v>
       </c>
@@ -19789,7 +19801,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>19</v>
       </c>
@@ -19827,7 +19839,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>19</v>
       </c>
@@ -19865,7 +19877,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
         <v>19</v>
       </c>
@@ -19903,7 +19915,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>19</v>
       </c>
@@ -19941,7 +19953,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>19</v>
       </c>
@@ -19979,7 +19991,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>19</v>
       </c>
@@ -20017,7 +20029,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
         <v>19</v>
       </c>
@@ -20055,7 +20067,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
         <v>19</v>
       </c>
@@ -20093,7 +20105,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
         <v>19</v>
       </c>
@@ -20131,7 +20143,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
         <v>19</v>
       </c>
@@ -20169,7 +20181,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
         <v>19</v>
       </c>
@@ -20207,7 +20219,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>19</v>
       </c>
@@ -20245,7 +20257,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>19</v>
       </c>
@@ -20283,7 +20295,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
         <v>19</v>
       </c>
@@ -20321,7 +20333,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>19</v>
       </c>
@@ -20359,7 +20371,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>19</v>
       </c>
@@ -20397,7 +20409,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
         <v>19</v>
       </c>
@@ -20435,7 +20447,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
         <v>19</v>
       </c>
@@ -20473,7 +20485,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
         <v>19</v>
       </c>
@@ -20511,7 +20523,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
         <v>19</v>
       </c>
@@ -20549,7 +20561,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
         <v>19</v>
       </c>
@@ -20587,7 +20599,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
         <v>19</v>
       </c>
@@ -20625,7 +20637,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
         <v>19</v>
       </c>
@@ -20663,7 +20675,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
         <v>19</v>
       </c>
@@ -20701,7 +20713,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
         <v>19</v>
       </c>
@@ -20739,7 +20751,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
         <v>19</v>
       </c>
@@ -20777,7 +20789,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
         <v>19</v>
       </c>
@@ -20815,7 +20827,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
         <v>19</v>
       </c>
@@ -20853,7 +20865,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
         <v>19</v>
       </c>
@@ -20891,7 +20903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
         <v>19</v>
       </c>
@@ -20929,7 +20941,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
         <v>19</v>
       </c>
@@ -20967,7 +20979,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
         <v>19</v>
       </c>
@@ -21005,7 +21017,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
         <v>19</v>
       </c>
@@ -21043,7 +21055,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
         <v>19</v>
       </c>
@@ -21081,7 +21093,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
         <v>19</v>
       </c>
@@ -21119,7 +21131,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
         <v>19</v>
       </c>
@@ -21157,7 +21169,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
         <v>19</v>
       </c>
@@ -21195,7 +21207,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
         <v>19</v>
       </c>
@@ -21233,7 +21245,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
         <v>19</v>
       </c>
@@ -21271,7 +21283,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
         <v>19</v>
       </c>
@@ -21309,7 +21321,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
         <v>19</v>
       </c>
@@ -21347,7 +21359,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
         <v>19</v>
       </c>
@@ -21385,7 +21397,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
         <v>19</v>
       </c>
@@ -21423,7 +21435,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
         <v>19</v>
       </c>
@@ -21461,7 +21473,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
         <v>19</v>
       </c>
@@ -21499,7 +21511,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
         <v>19</v>
       </c>
@@ -21537,7 +21549,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
         <v>19</v>
       </c>
@@ -21575,7 +21587,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
         <v>19</v>
       </c>
@@ -21613,7 +21625,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
         <v>19</v>
       </c>
@@ -21651,7 +21663,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
         <v>19</v>
       </c>
@@ -21689,7 +21701,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
         <v>19</v>
       </c>
@@ -21727,7 +21739,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
         <v>19</v>
       </c>
@@ -21765,7 +21777,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
         <v>19</v>
       </c>
@@ -21803,7 +21815,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
         <v>19</v>
       </c>
@@ -21841,7 +21853,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
         <v>19</v>
       </c>
@@ -21879,7 +21891,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>19</v>
       </c>
@@ -21917,7 +21929,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
         <v>19</v>
       </c>
@@ -21955,7 +21967,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
         <v>19</v>
       </c>
@@ -21993,7 +22005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
         <v>19</v>
       </c>
@@ -22031,7 +22043,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
         <v>19</v>
       </c>
@@ -22069,7 +22081,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
         <v>19</v>
       </c>
@@ -22107,7 +22119,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
         <v>19</v>
       </c>
@@ -22145,7 +22157,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
         <v>19</v>
       </c>
@@ -22183,7 +22195,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
         <v>19</v>
       </c>
@@ -22221,7 +22233,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
         <v>19</v>
       </c>
@@ -22259,7 +22271,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
         <v>19</v>
       </c>
@@ -22297,7 +22309,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
         <v>19</v>
       </c>
@@ -22335,7 +22347,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
         <v>19</v>
       </c>
@@ -22373,7 +22385,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
         <v>19</v>
       </c>
@@ -22411,7 +22423,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
         <v>19</v>
       </c>
@@ -22449,7 +22461,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
         <v>19</v>
       </c>
@@ -22487,7 +22499,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
         <v>19</v>
       </c>
@@ -22525,7 +22537,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
         <v>19</v>
       </c>
@@ -22563,7 +22575,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
         <v>19</v>
       </c>
@@ -22601,7 +22613,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
         <v>19</v>
       </c>
@@ -22639,7 +22651,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
         <v>19</v>
       </c>
@@ -22677,7 +22689,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
         <v>19</v>
       </c>
@@ -22715,7 +22727,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
         <v>19</v>
       </c>
@@ -22753,7 +22765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
         <v>19</v>
       </c>
@@ -22791,7 +22803,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
         <v>19</v>
       </c>
@@ -22829,7 +22841,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="497" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
         <v>19</v>
       </c>
@@ -22867,7 +22879,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
         <v>19</v>
       </c>
@@ -22905,7 +22917,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
         <v>19</v>
       </c>
@@ -22943,7 +22955,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
         <v>19</v>
       </c>
@@ -22981,7 +22993,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
         <v>19</v>
       </c>
@@ -23019,7 +23031,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
         <v>19</v>
       </c>
@@ -23057,7 +23069,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
         <v>19</v>
       </c>
@@ -23095,7 +23107,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
         <v>19</v>
       </c>
@@ -23133,7 +23145,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
         <v>19</v>
       </c>
@@ -23171,7 +23183,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
         <v>19</v>
       </c>
@@ -23209,7 +23221,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
         <v>19</v>
       </c>
@@ -23247,7 +23259,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
         <v>19</v>
       </c>
@@ -23285,7 +23297,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
         <v>19</v>
       </c>
@@ -23323,7 +23335,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
         <v>19</v>
       </c>
@@ -23361,7 +23373,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
         <v>19</v>
       </c>
@@ -23399,7 +23411,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
         <v>19</v>
       </c>
@@ -23437,7 +23449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
         <v>19</v>
       </c>
@@ -23475,7 +23487,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
         <v>19</v>
       </c>
@@ -23513,7 +23525,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
         <v>19</v>
       </c>
@@ -23551,7 +23563,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
         <v>19</v>
       </c>
@@ -23589,7 +23601,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
         <v>19</v>
       </c>
@@ -23627,7 +23639,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
         <v>19</v>
       </c>
@@ -23665,7 +23677,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
         <v>19</v>
       </c>
@@ -23703,7 +23715,7 @@
         <v>28.3</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
         <v>19</v>
       </c>
@@ -23741,7 +23753,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
         <v>19</v>
       </c>
@@ -23779,7 +23791,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
         <v>19</v>
       </c>
@@ -23817,7 +23829,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
         <v>19</v>
       </c>
@@ -23855,7 +23867,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
         <v>19</v>
       </c>
@@ -23893,7 +23905,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
         <v>19</v>
       </c>
@@ -23931,7 +23943,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
         <v>19</v>
       </c>
@@ -23969,7 +23981,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
         <v>19</v>
       </c>
@@ -24007,7 +24019,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
         <v>19</v>
       </c>
@@ -24045,7 +24057,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="529" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
         <v>19</v>
       </c>
@@ -24083,7 +24095,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="530" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
         <v>19</v>
       </c>
@@ -24121,7 +24133,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="531" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="s">
         <v>19</v>
       </c>
@@ -24159,7 +24171,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
         <v>19</v>
       </c>
@@ -24197,7 +24209,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="s">
         <v>19</v>
       </c>
@@ -24235,7 +24247,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F534" s="1" t="s">
         <v>226</v>
       </c>
@@ -24255,7 +24267,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F535" s="1" t="s">
         <v>718</v>
       </c>
@@ -24275,7 +24287,7 @@
         <v>2783.8</v>
       </c>
     </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
         <v>19</v>
       </c>
@@ -24313,7 +24325,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="537" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A537" s="1" t="s">
         <v>19</v>
       </c>
@@ -24351,7 +24363,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
         <v>19</v>
       </c>
@@ -24389,7 +24401,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A539" s="1" t="s">
         <v>19</v>
       </c>
@@ -24427,7 +24439,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
         <v>19</v>
       </c>
@@ -24465,7 +24477,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="541" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A541" s="1" t="s">
         <v>19</v>
       </c>
@@ -24503,7 +24515,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="542" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
         <v>19</v>
       </c>
@@ -24541,7 +24553,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="543" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A543" s="1" t="s">
         <v>19</v>
       </c>
@@ -24579,7 +24591,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="544" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
         <v>19</v>
       </c>
@@ -24617,7 +24629,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A545" s="1" t="s">
         <v>19</v>
       </c>
@@ -24655,7 +24667,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
         <v>19</v>
       </c>
@@ -24693,7 +24705,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A547" s="1" t="s">
         <v>19</v>
       </c>
@@ -24731,7 +24743,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
         <v>19</v>
       </c>
@@ -24769,7 +24781,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A549" s="1" t="s">
         <v>19</v>
       </c>
@@ -24807,7 +24819,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
         <v>19</v>
       </c>
@@ -24845,7 +24857,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A551" s="1" t="s">
         <v>19</v>
       </c>
@@ -24883,7 +24895,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
         <v>19</v>
       </c>
@@ -24921,7 +24933,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A553" s="1" t="s">
         <v>19</v>
       </c>
@@ -24959,7 +24971,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
         <v>19</v>
       </c>
@@ -24997,7 +25009,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A555" s="1" t="s">
         <v>19</v>
       </c>
@@ -25035,7 +25047,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
         <v>19</v>
       </c>
@@ -25073,7 +25085,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A557" s="1" t="s">
         <v>19</v>
       </c>
@@ -25111,7 +25123,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
         <v>19</v>
       </c>
@@ -25149,7 +25161,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A559" s="1" t="s">
         <v>19</v>
       </c>
@@ -25187,7 +25199,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
         <v>19</v>
       </c>
@@ -25225,7 +25237,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A561" s="1" t="s">
         <v>19</v>
       </c>
@@ -25263,7 +25275,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
         <v>19</v>
       </c>
@@ -25301,7 +25313,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="563" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A563" s="1" t="s">
         <v>19</v>
       </c>
@@ -25339,7 +25351,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
         <v>19</v>
       </c>
@@ -25377,7 +25389,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A565" s="1" t="s">
         <v>19</v>
       </c>
@@ -25415,7 +25427,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
         <v>19</v>
       </c>
@@ -25453,7 +25465,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A567" s="1" t="s">
         <v>19</v>
       </c>
@@ -25491,7 +25503,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="568" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
         <v>19</v>
       </c>
@@ -25529,7 +25541,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="569" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A569" s="1" t="s">
         <v>19</v>
       </c>
@@ -25567,7 +25579,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
         <v>19</v>
       </c>
@@ -25605,7 +25617,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A571" s="1" t="s">
         <v>19</v>
       </c>
@@ -25643,7 +25655,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="572" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
         <v>19</v>
       </c>
@@ -25681,7 +25693,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="573" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A573" s="1" t="s">
         <v>19</v>
       </c>
@@ -25719,7 +25731,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
         <v>19</v>
       </c>
@@ -25757,7 +25769,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="575" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A575" s="1" t="s">
         <v>19</v>
       </c>
@@ -25795,7 +25807,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="576" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
         <v>19</v>
       </c>
@@ -25833,7 +25845,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="577" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A577" s="1" t="s">
         <v>19</v>
       </c>
@@ -25871,7 +25883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="578" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
         <v>19</v>
       </c>
@@ -25909,7 +25921,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="579" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A579" s="1" t="s">
         <v>19</v>
       </c>
@@ -25947,7 +25959,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="580" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
         <v>19</v>
       </c>
@@ -25985,7 +25997,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="581" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A581" s="1" t="s">
         <v>19</v>
       </c>
@@ -26023,7 +26035,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="582" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
         <v>19</v>
       </c>
@@ -26061,7 +26073,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="583" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A583" s="1" t="s">
         <v>19</v>
       </c>
@@ -26099,7 +26111,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="584" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
         <v>19</v>
       </c>
@@ -26137,7 +26149,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="585" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A585" s="1" t="s">
         <v>19</v>
       </c>
@@ -26175,7 +26187,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="586" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
         <v>19</v>
       </c>
@@ -26213,7 +26225,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="587" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A587" s="1" t="s">
         <v>19</v>
       </c>
@@ -26251,7 +26263,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="588" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
         <v>19</v>
       </c>
@@ -26289,7 +26301,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="589" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A589" s="1" t="s">
         <v>19</v>
       </c>
@@ -26327,7 +26339,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="590" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
         <v>19</v>
       </c>
@@ -26365,7 +26377,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="591" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A591" s="1" t="s">
         <v>19</v>
       </c>
@@ -26403,7 +26415,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="592" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
         <v>19</v>
       </c>
@@ -26441,7 +26453,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="593" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A593" s="1" t="s">
         <v>19</v>
       </c>
@@ -26479,7 +26491,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="594" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
         <v>19</v>
       </c>
@@ -26517,7 +26529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="595" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A595" s="1" t="s">
         <v>19</v>
       </c>
@@ -26555,7 +26567,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="596" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
         <v>19</v>
       </c>
@@ -26593,7 +26605,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="597" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A597" s="1" t="s">
         <v>19</v>
       </c>
@@ -26631,7 +26643,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="598" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
         <v>19</v>
       </c>
@@ -26669,7 +26681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="599" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A599" s="1" t="s">
         <v>19</v>
       </c>
@@ -26707,7 +26719,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="600" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A600" s="1" t="s">
         <v>19</v>
       </c>
@@ -26745,7 +26757,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="601" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A601" s="1" t="s">
         <v>19</v>
       </c>
@@ -26783,7 +26795,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="602" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="s">
         <v>19</v>
       </c>
@@ -26821,7 +26833,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="603" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A603" s="1" t="s">
         <v>19</v>
       </c>
@@ -26859,7 +26871,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="604" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
         <v>19</v>
       </c>
@@ -26897,7 +26909,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="605" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A605" s="1" t="s">
         <v>19</v>
       </c>
@@ -26935,7 +26947,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="606" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="s">
         <v>19</v>
       </c>
@@ -26973,7 +26985,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="607" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A607" s="1" t="s">
         <v>19</v>
       </c>
@@ -27011,7 +27023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="608" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A608" s="1" t="s">
         <v>19</v>
       </c>
@@ -27049,7 +27061,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="609" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A609" s="1" t="s">
         <v>19</v>
       </c>
@@ -27087,7 +27099,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="610" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A610" s="1" t="s">
         <v>19</v>
       </c>
@@ -27125,7 +27137,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="611" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A611" s="1" t="s">
         <v>19</v>
       </c>
@@ -27163,7 +27175,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="612" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A612" s="1" t="s">
         <v>19</v>
       </c>
@@ -27201,7 +27213,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="613" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A613" s="1" t="s">
         <v>19</v>
       </c>
@@ -27239,7 +27251,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="614" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A614" s="1" t="s">
         <v>19</v>
       </c>
@@ -27277,7 +27289,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="615" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A615" s="1" t="s">
         <v>19</v>
       </c>
@@ -27315,7 +27327,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="616" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A616" s="1" t="s">
         <v>19</v>
       </c>
@@ -27353,7 +27365,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="617" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A617" s="1" t="s">
         <v>19</v>
       </c>
@@ -27391,7 +27403,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="618" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A618" s="1" t="s">
         <v>19</v>
       </c>
@@ -27429,7 +27441,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="619" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A619" s="1" t="s">
         <v>19</v>
       </c>
@@ -27467,7 +27479,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="620" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A620" s="1" t="s">
         <v>19</v>
       </c>
@@ -27505,7 +27517,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="621" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A621" s="1" t="s">
         <v>19</v>
       </c>
@@ -27543,7 +27555,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="622" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A622" s="1" t="s">
         <v>19</v>
       </c>
@@ -27581,7 +27593,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="623" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A623" s="1" t="s">
         <v>19</v>
       </c>
@@ -27619,7 +27631,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="624" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A624" s="1" t="s">
         <v>19</v>
       </c>
@@ -27657,7 +27669,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="625" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F625" s="1" t="s">
         <v>226</v>
       </c>
@@ -27677,7 +27689,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="626" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F626" s="1" t="s">
         <v>214</v>
       </c>
@@ -27697,7 +27709,7 @@
         <v>1851.6</v>
       </c>
     </row>
-    <row r="627" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A627" s="1" t="s">
         <v>19</v>
       </c>
@@ -27735,7 +27747,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="628" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A628" s="1" t="s">
         <v>19</v>
       </c>
@@ -27773,7 +27785,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="629" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A629" s="1" t="s">
         <v>19</v>
       </c>
@@ -27811,7 +27823,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="630" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A630" s="1" t="s">
         <v>19</v>
       </c>
@@ -27849,7 +27861,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="631" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A631" s="1" t="s">
         <v>19</v>
       </c>
@@ -27887,7 +27899,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="632" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A632" s="1" t="s">
         <v>19</v>
       </c>
@@ -27925,7 +27937,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="633" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A633" s="1" t="s">
         <v>19</v>
       </c>
@@ -27963,7 +27975,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="634" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="s">
         <v>19</v>
       </c>
@@ -28001,7 +28013,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="635" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A635" s="1" t="s">
         <v>19</v>
       </c>
@@ -28039,7 +28051,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="636" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A636" s="1" t="s">
         <v>19</v>
       </c>
@@ -28077,7 +28089,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="637" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A637" s="1" t="s">
         <v>19</v>
       </c>
@@ -28115,7 +28127,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="638" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A638" s="1" t="s">
         <v>19</v>
       </c>
@@ -28153,7 +28165,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="639" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A639" s="1" t="s">
         <v>19</v>
       </c>
@@ -28191,7 +28203,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="640" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A640" s="1" t="s">
         <v>19</v>
       </c>
@@ -28229,7 +28241,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="641" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A641" s="1" t="s">
         <v>19</v>
       </c>
@@ -28267,7 +28279,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="642" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A642" s="1" t="s">
         <v>19</v>
       </c>
@@ -28305,7 +28317,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="643" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A643" s="1" t="s">
         <v>19</v>
       </c>
@@ -28343,7 +28355,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="644" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A644" s="1" t="s">
         <v>19</v>
       </c>
@@ -28381,7 +28393,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="645" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A645" s="1" t="s">
         <v>19</v>
       </c>
@@ -28419,7 +28431,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="646" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A646" s="1" t="s">
         <v>19</v>
       </c>
@@ -28457,7 +28469,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="647" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A647" s="1" t="s">
         <v>19</v>
       </c>
@@ -28495,7 +28507,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="648" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A648" s="1" t="s">
         <v>19</v>
       </c>
@@ -28533,7 +28545,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="649" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A649" s="1" t="s">
         <v>19</v>
       </c>
@@ -28571,7 +28583,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="650" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A650" s="1" t="s">
         <v>19</v>
       </c>
@@ -28609,7 +28621,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="651" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A651" s="1" t="s">
         <v>19</v>
       </c>
@@ -28647,7 +28659,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="652" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A652" s="1" t="s">
         <v>19</v>
       </c>
@@ -28685,7 +28697,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="653" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A653" s="1" t="s">
         <v>19</v>
       </c>
@@ -28723,7 +28735,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="654" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A654" s="1" t="s">
         <v>19</v>
       </c>
@@ -28761,7 +28773,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="655" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A655" s="1" t="s">
         <v>19</v>
       </c>
@@ -28799,7 +28811,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="656" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A656" s="1" t="s">
         <v>19</v>
       </c>
@@ -28837,7 +28849,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="657" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A657" s="1" t="s">
         <v>19</v>
       </c>
@@ -28875,7 +28887,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="658" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A658" s="1" t="s">
         <v>19</v>
       </c>
@@ -28913,7 +28925,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="659" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A659" s="1" t="s">
         <v>19</v>
       </c>
@@ -28951,7 +28963,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="660" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A660" s="1" t="s">
         <v>19</v>
       </c>
@@ -28989,7 +29001,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="661" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A661" s="1" t="s">
         <v>19</v>
       </c>
@@ -29027,7 +29039,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="662" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A662" s="1" t="s">
         <v>19</v>
       </c>
@@ -29065,7 +29077,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="663" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A663" s="1" t="s">
         <v>19</v>
       </c>
@@ -29103,7 +29115,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="664" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A664" s="1" t="s">
         <v>19</v>
       </c>
@@ -29141,7 +29153,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="665" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A665" s="1" t="s">
         <v>19</v>
       </c>
@@ -29179,7 +29191,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="666" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A666" s="1" t="s">
         <v>19</v>
       </c>
@@ -29217,7 +29229,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="667" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A667" s="1" t="s">
         <v>19</v>
       </c>
@@ -29255,7 +29267,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="668" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A668" s="1" t="s">
         <v>19</v>
       </c>
@@ -29293,7 +29305,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="669" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A669" s="1" t="s">
         <v>19</v>
       </c>
@@ -29331,7 +29343,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="670" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A670" s="1" t="s">
         <v>19</v>
       </c>
@@ -29369,7 +29381,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="671" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A671" s="1" t="s">
         <v>19</v>
       </c>
@@ -29407,7 +29419,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="672" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A672" s="1" t="s">
         <v>19</v>
       </c>
@@ -29445,7 +29457,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="673" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A673" s="1" t="s">
         <v>19</v>
       </c>
@@ -29483,7 +29495,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="674" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A674" s="1" t="s">
         <v>19</v>
       </c>
@@ -29521,7 +29533,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="675" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A675" s="1" t="s">
         <v>19</v>
       </c>
@@ -29559,7 +29571,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="676" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A676" s="1" t="s">
         <v>19</v>
       </c>
@@ -29597,7 +29609,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="677" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A677" s="1" t="s">
         <v>19</v>
       </c>
@@ -29635,7 +29647,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="678" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A678" s="1" t="s">
         <v>19</v>
       </c>
@@ -29673,7 +29685,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="679" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A679" s="1" t="s">
         <v>19</v>
       </c>
@@ -29711,7 +29723,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="680" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A680" s="1" t="s">
         <v>19</v>
       </c>
@@ -29749,7 +29761,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="681" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A681" s="1" t="s">
         <v>19</v>
       </c>
@@ -29787,7 +29799,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="682" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A682" s="1" t="s">
         <v>19</v>
       </c>
@@ -29825,7 +29837,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="683" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A683" s="1" t="s">
         <v>19</v>
       </c>
@@ -29863,7 +29875,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="684" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A684" s="1" t="s">
         <v>19</v>
       </c>
@@ -29901,7 +29913,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="685" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A685" s="1" t="s">
         <v>19</v>
       </c>
@@ -29939,7 +29951,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="686" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A686" s="1" t="s">
         <v>19</v>
       </c>
@@ -29977,7 +29989,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="687" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A687" s="1" t="s">
         <v>19</v>
       </c>
@@ -30015,7 +30027,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="688" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A688" s="1" t="s">
         <v>19</v>
       </c>
@@ -30053,7 +30065,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="689" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A689" s="1" t="s">
         <v>19</v>
       </c>
@@ -30091,7 +30103,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="690" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A690" s="1" t="s">
         <v>19</v>
       </c>
@@ -30129,7 +30141,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="691" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A691" s="1" t="s">
         <v>19</v>
       </c>
@@ -30167,7 +30179,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="692" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A692" s="1" t="s">
         <v>19</v>
       </c>
@@ -30205,7 +30217,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="693" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A693" s="1" t="s">
         <v>19</v>
       </c>
@@ -30243,7 +30255,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="694" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A694" s="1" t="s">
         <v>19</v>
       </c>
@@ -30281,7 +30293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="695" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A695" s="1" t="s">
         <v>19</v>
       </c>
@@ -30319,7 +30331,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="696" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A696" s="1" t="s">
         <v>19</v>
       </c>
@@ -30357,7 +30369,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="697" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A697" s="1" t="s">
         <v>19</v>
       </c>
@@ -30395,7 +30407,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="698" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A698" s="1" t="s">
         <v>19</v>
       </c>
@@ -30433,7 +30445,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="699" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A699" s="1" t="s">
         <v>19</v>
       </c>
@@ -30471,7 +30483,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="700" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A700" s="1" t="s">
         <v>19</v>
       </c>
@@ -30509,7 +30521,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="701" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A701" s="1" t="s">
         <v>19</v>
       </c>
@@ -30547,7 +30559,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="702" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A702" s="1" t="s">
         <v>19</v>
       </c>
@@ -30585,7 +30597,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="703" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A703" s="1" t="s">
         <v>19</v>
       </c>
@@ -30623,7 +30635,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="704" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A704" s="1" t="s">
         <v>19</v>
       </c>
@@ -30661,7 +30673,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="705" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A705" s="1" t="s">
         <v>19</v>
       </c>
@@ -30699,7 +30711,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="706" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A706" s="1" t="s">
         <v>19</v>
       </c>
@@ -30737,7 +30749,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="707" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A707" s="1" t="s">
         <v>19</v>
       </c>
@@ -30775,7 +30787,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="708" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A708" s="1" t="s">
         <v>19</v>
       </c>
@@ -30813,7 +30825,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="709" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A709" s="1" t="s">
         <v>19</v>
       </c>
@@ -30851,7 +30863,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="710" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A710" s="1" t="s">
         <v>19</v>
       </c>
@@ -30889,7 +30901,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="711" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A711" s="1" t="s">
         <v>19</v>
       </c>
@@ -30927,7 +30939,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="712" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A712" s="1" t="s">
         <v>19</v>
       </c>
@@ -30965,7 +30977,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="713" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A713" s="1" t="s">
         <v>19</v>
       </c>
@@ -31003,7 +31015,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="714" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A714" s="1" t="s">
         <v>19</v>
       </c>
@@ -31041,7 +31053,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="715" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A715" s="1" t="s">
         <v>19</v>
       </c>
@@ -31079,7 +31091,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="716" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A716" s="1" t="s">
         <v>19</v>
       </c>
@@ -31117,7 +31129,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="717" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A717" s="1" t="s">
         <v>19</v>
       </c>
@@ -31155,7 +31167,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="718" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A718" s="1" t="s">
         <v>19</v>
       </c>
@@ -31193,7 +31205,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="719" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A719" s="1" t="s">
         <v>19</v>
       </c>
@@ -31231,7 +31243,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="720" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A720" s="1" t="s">
         <v>19</v>
       </c>
@@ -31269,7 +31281,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="721" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A721" s="1" t="s">
         <v>19</v>
       </c>
@@ -31307,7 +31319,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="722" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A722" s="1" t="s">
         <v>19</v>
       </c>
@@ -31345,7 +31357,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="723" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A723" s="1" t="s">
         <v>19</v>
       </c>
@@ -31383,7 +31395,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="724" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A724" s="1" t="s">
         <v>19</v>
       </c>
@@ -31421,7 +31433,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="725" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A725" s="1" t="s">
         <v>19</v>
       </c>
@@ -31459,7 +31471,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="726" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A726" s="1" t="s">
         <v>19</v>
       </c>
@@ -31497,7 +31509,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="727" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A727" s="1" t="s">
         <v>19</v>
       </c>
@@ -31535,7 +31547,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="728" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A728" s="1" t="s">
         <v>19</v>
       </c>
@@ -31573,7 +31585,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="729" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A729" s="1" t="s">
         <v>19</v>
       </c>
@@ -31611,7 +31623,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="730" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A730" s="1" t="s">
         <v>19</v>
       </c>
@@ -31649,7 +31661,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="731" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A731" s="1" t="s">
         <v>19</v>
       </c>
@@ -31687,7 +31699,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="732" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A732" s="1" t="s">
         <v>19</v>
       </c>
@@ -31725,7 +31737,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="733" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A733" s="1" t="s">
         <v>19</v>
       </c>
@@ -31763,7 +31775,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="734" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A734" s="1" t="s">
         <v>19</v>
       </c>
@@ -31801,7 +31813,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="735" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A735" s="1" t="s">
         <v>19</v>
       </c>
@@ -31839,7 +31851,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="736" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A736" s="1" t="s">
         <v>19</v>
       </c>
@@ -31877,7 +31889,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="737" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A737" s="1" t="s">
         <v>19</v>
       </c>
@@ -31915,7 +31927,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="738" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A738" s="1" t="s">
         <v>19</v>
       </c>
@@ -31953,7 +31965,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="739" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A739" s="1" t="s">
         <v>19</v>
       </c>
@@ -31991,7 +32003,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="740" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A740" s="1" t="s">
         <v>19</v>
       </c>
@@ -32029,7 +32041,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="741" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A741" s="1" t="s">
         <v>19</v>
       </c>
@@ -32067,7 +32079,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="742" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A742" s="1" t="s">
         <v>19</v>
       </c>
@@ -32105,7 +32117,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="743" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A743" s="1" t="s">
         <v>19</v>
       </c>
@@ -32143,7 +32155,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="744" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A744" s="1" t="s">
         <v>19</v>
       </c>
@@ -32181,7 +32193,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="745" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A745" s="1" t="s">
         <v>19</v>
       </c>
@@ -32219,7 +32231,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="746" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A746" s="1" t="s">
         <v>19</v>
       </c>
@@ -32257,7 +32269,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="747" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A747" s="1" t="s">
         <v>19</v>
       </c>
@@ -32295,7 +32307,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="748" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A748" s="1" t="s">
         <v>19</v>
       </c>
@@ -32333,7 +32345,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="749" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A749" s="1" t="s">
         <v>19</v>
       </c>
@@ -32371,7 +32383,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="750" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A750" s="1" t="s">
         <v>19</v>
       </c>
@@ -32409,7 +32421,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="751" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A751" s="1" t="s">
         <v>19</v>
       </c>
@@ -32447,7 +32459,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="752" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A752" s="1" t="s">
         <v>19</v>
       </c>
@@ -32485,7 +32497,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="753" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A753" s="1" t="s">
         <v>19</v>
       </c>
@@ -32523,7 +32535,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="754" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A754" s="1" t="s">
         <v>19</v>
       </c>
@@ -32561,7 +32573,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="755" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A755" s="1" t="s">
         <v>19</v>
       </c>
@@ -32599,7 +32611,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="756" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A756" s="1" t="s">
         <v>19</v>
       </c>
@@ -32637,7 +32649,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="757" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A757" s="1" t="s">
         <v>19</v>
       </c>
@@ -32675,7 +32687,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="758" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A758" s="1" t="s">
         <v>19</v>
       </c>
@@ -32713,7 +32725,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="759" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A759" s="1" t="s">
         <v>19</v>
       </c>
@@ -32751,7 +32763,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="760" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A760" s="1" t="s">
         <v>19</v>
       </c>
@@ -32789,7 +32801,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="761" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A761" s="1" t="s">
         <v>19</v>
       </c>
@@ -32827,7 +32839,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="762" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A762" s="1" t="s">
         <v>19</v>
       </c>
@@ -32865,7 +32877,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="763" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A763" s="1" t="s">
         <v>19</v>
       </c>
@@ -32903,7 +32915,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="764" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A764" s="1" t="s">
         <v>19</v>
       </c>
@@ -32941,7 +32953,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="765" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A765" s="1" t="s">
         <v>19</v>
       </c>
@@ -32979,7 +32991,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="766" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A766" s="1" t="s">
         <v>19</v>
       </c>
@@ -33017,7 +33029,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="767" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A767" s="1" t="s">
         <v>19</v>
       </c>
@@ -33055,7 +33067,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="768" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A768" s="1" t="s">
         <v>19</v>
       </c>
@@ -33093,7 +33105,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="769" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A769" s="1" t="s">
         <v>19</v>
       </c>
@@ -33131,7 +33143,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="770" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A770" s="1" t="s">
         <v>19</v>
       </c>
@@ -33169,7 +33181,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="771" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A771" s="1" t="s">
         <v>19</v>
       </c>
@@ -33207,7 +33219,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="772" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A772" s="1" t="s">
         <v>19</v>
       </c>
@@ -33245,7 +33257,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="773" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A773" s="1" t="s">
         <v>19</v>
       </c>
@@ -33283,7 +33295,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="774" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A774" s="1" t="s">
         <v>19</v>
       </c>
@@ -33321,7 +33333,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="775" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A775" s="1" t="s">
         <v>19</v>
       </c>
@@ -33359,7 +33371,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="776" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A776" s="1" t="s">
         <v>19</v>
       </c>
@@ -33397,7 +33409,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="777" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A777" s="1" t="s">
         <v>19</v>
       </c>
@@ -33435,7 +33447,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="778" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A778" s="1" t="s">
         <v>19</v>
       </c>
@@ -33473,7 +33485,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="779" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A779" s="1" t="s">
         <v>19</v>
       </c>
@@ -33511,7 +33523,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="780" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A780" s="1" t="s">
         <v>19</v>
       </c>
@@ -33549,7 +33561,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="781" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A781" s="1" t="s">
         <v>19</v>
       </c>
@@ -33587,7 +33599,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="782" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A782" s="1" t="s">
         <v>19</v>
       </c>
@@ -33625,7 +33637,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="783" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A783" s="1" t="s">
         <v>19</v>
       </c>
@@ -33663,7 +33675,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="784" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A784" s="1" t="s">
         <v>19</v>
       </c>
@@ -33701,7 +33713,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="785" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A785" s="1" t="s">
         <v>19</v>
       </c>
@@ -33739,7 +33751,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="786" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A786" s="1" t="s">
         <v>19</v>
       </c>
@@ -33777,7 +33789,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="787" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A787" s="1" t="s">
         <v>19</v>
       </c>
@@ -33815,7 +33827,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="788" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A788" s="1" t="s">
         <v>19</v>
       </c>
@@ -33853,7 +33865,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="789" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A789" s="1" t="s">
         <v>19</v>
       </c>
@@ -33891,7 +33903,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="790" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A790" s="1" t="s">
         <v>19</v>
       </c>
@@ -33929,7 +33941,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="791" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A791" s="1" t="s">
         <v>19</v>
       </c>
@@ -33967,7 +33979,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="792" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A792" s="1" t="s">
         <v>19</v>
       </c>
@@ -34005,7 +34017,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="793" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A793" s="1" t="s">
         <v>19</v>
       </c>
@@ -34043,7 +34055,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="794" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A794" s="1" t="s">
         <v>19</v>
       </c>
@@ -34081,7 +34093,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="795" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A795" s="1" t="s">
         <v>19</v>
       </c>
@@ -34119,7 +34131,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="796" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A796" s="1" t="s">
         <v>19</v>
       </c>
@@ -34157,7 +34169,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="797" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A797" s="1" t="s">
         <v>19</v>
       </c>
@@ -34195,7 +34207,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="798" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A798" s="1" t="s">
         <v>19</v>
       </c>
@@ -34233,7 +34245,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="799" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A799" s="1" t="s">
         <v>19</v>
       </c>
@@ -34271,7 +34283,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="800" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A800" s="1" t="s">
         <v>19</v>
       </c>
@@ -34309,7 +34321,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="801" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A801" s="1" t="s">
         <v>19</v>
       </c>
@@ -34347,7 +34359,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="802" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A802" s="1" t="s">
         <v>19</v>
       </c>
@@ -34385,7 +34397,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="803" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A803" s="1" t="s">
         <v>19</v>
       </c>
@@ -34423,7 +34435,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="804" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A804" s="1" t="s">
         <v>19</v>
       </c>
@@ -34461,7 +34473,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="805" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A805" s="1" t="s">
         <v>19</v>
       </c>
@@ -34499,7 +34511,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="806" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A806" s="1" t="s">
         <v>19</v>
       </c>
@@ -34537,7 +34549,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="807" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A807" s="1" t="s">
         <v>19</v>
       </c>
@@ -34575,7 +34587,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="808" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A808" s="1" t="s">
         <v>19</v>
       </c>
@@ -34613,7 +34625,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="809" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A809" s="1" t="s">
         <v>19</v>
       </c>
@@ -34651,7 +34663,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="810" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A810" s="1" t="s">
         <v>19</v>
       </c>
@@ -34689,7 +34701,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="811" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A811" s="1" t="s">
         <v>19</v>
       </c>
@@ -34727,7 +34739,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="812" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A812" s="1" t="s">
         <v>19</v>
       </c>
@@ -34765,7 +34777,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="813" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A813" s="1" t="s">
         <v>19</v>
       </c>
@@ -34803,7 +34815,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="814" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A814" s="1" t="s">
         <v>19</v>
       </c>
@@ -34841,7 +34853,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="815" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A815" s="1" t="s">
         <v>19</v>
       </c>
@@ -34879,7 +34891,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="816" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A816" s="1" t="s">
         <v>19</v>
       </c>
@@ -34917,7 +34929,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="817" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A817" s="1" t="s">
         <v>19</v>
       </c>
@@ -34955,7 +34967,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="818" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A818" s="1" t="s">
         <v>19</v>
       </c>
@@ -34993,7 +35005,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="819" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A819" s="1" t="s">
         <v>19</v>
       </c>
@@ -35031,7 +35043,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="820" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A820" s="1" t="s">
         <v>19</v>
       </c>
@@ -35069,7 +35081,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="821" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A821" s="1" t="s">
         <v>19</v>
       </c>
@@ -35107,7 +35119,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="822" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A822" s="1" t="s">
         <v>19</v>
       </c>
@@ -35145,7 +35157,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="823" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A823" s="1" t="s">
         <v>19</v>
       </c>
@@ -35183,7 +35195,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="824" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A824" s="1" t="s">
         <v>19</v>
       </c>
@@ -35221,7 +35233,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="825" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A825" s="1" t="s">
         <v>19</v>
       </c>
@@ -35259,7 +35271,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="826" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A826" s="1" t="s">
         <v>19</v>
       </c>
@@ -35297,7 +35309,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="827" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A827" s="1" t="s">
         <v>19</v>
       </c>
@@ -35335,7 +35347,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="828" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A828" s="1" t="s">
         <v>19</v>
       </c>
@@ -35373,7 +35385,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="829" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A829" s="1" t="s">
         <v>19</v>
       </c>
@@ -35411,7 +35423,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="830" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A830" s="1" t="s">
         <v>19</v>
       </c>
@@ -35449,7 +35461,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="831" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A831" s="1" t="s">
         <v>19</v>
       </c>
@@ -35487,7 +35499,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="832" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A832" s="1" t="s">
         <v>19</v>
       </c>
@@ -35525,7 +35537,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="833" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A833" s="1" t="s">
         <v>19</v>
       </c>
@@ -35563,7 +35575,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="834" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A834" s="1" t="s">
         <v>19</v>
       </c>
@@ -35601,7 +35613,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="835" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A835" s="1" t="s">
         <v>19</v>
       </c>
@@ -35639,7 +35651,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="836" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A836" s="1" t="s">
         <v>19</v>
       </c>
@@ -35677,7 +35689,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="837" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F837" s="1" t="s">
         <v>226</v>
       </c>
@@ -35697,7 +35709,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="838" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F838" s="1" t="s">
         <v>1073</v>
       </c>
@@ -35714,7 +35726,7 @@
         <v>4477.8</v>
       </c>
     </row>
-    <row r="839" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A839" s="1" t="s">
         <v>19</v>
       </c>
@@ -35752,7 +35764,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="840" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A840" s="1" t="s">
         <v>19</v>
       </c>
@@ -35790,7 +35802,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="841" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A841" s="1" t="s">
         <v>19</v>
       </c>
@@ -35828,7 +35840,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="842" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A842" s="1" t="s">
         <v>19</v>
       </c>
@@ -35866,7 +35878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="843" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A843" s="1" t="s">
         <v>19</v>
       </c>
@@ -35904,7 +35916,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="844" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A844" s="1" t="s">
         <v>19</v>
       </c>
@@ -35942,7 +35954,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="845" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A845" s="1" t="s">
         <v>19</v>
       </c>
@@ -35980,7 +35992,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="846" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A846" s="1" t="s">
         <v>19</v>
       </c>
@@ -36018,7 +36030,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="847" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A847" s="1" t="s">
         <v>19</v>
       </c>
@@ -36056,7 +36068,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="848" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A848" s="1" t="s">
         <v>19</v>
       </c>
@@ -36094,7 +36106,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="849" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A849" s="1" t="s">
         <v>19</v>
       </c>
@@ -36132,7 +36144,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="850" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A850" s="1" t="s">
         <v>19</v>
       </c>
@@ -36170,7 +36182,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="851" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A851" s="1" t="s">
         <v>19</v>
       </c>
@@ -36208,7 +36220,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="852" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A852" s="1" t="s">
         <v>19</v>
       </c>
@@ -36246,7 +36258,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="853" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A853" s="1" t="s">
         <v>19</v>
       </c>
@@ -36284,7 +36296,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="854" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A854" s="1" t="s">
         <v>19</v>
       </c>
@@ -36322,7 +36334,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="855" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A855" s="1" t="s">
         <v>19</v>
       </c>
@@ -36360,7 +36372,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="856" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A856" s="1" t="s">
         <v>19</v>
       </c>
@@ -36398,7 +36410,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="857" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A857" s="1" t="s">
         <v>19</v>
       </c>
@@ -36436,7 +36448,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="858" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A858" s="1" t="s">
         <v>19</v>
       </c>
@@ -36474,7 +36486,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="859" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A859" s="1" t="s">
         <v>19</v>
       </c>
@@ -36512,7 +36524,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="860" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A860" s="1" t="s">
         <v>19</v>
       </c>
@@ -36550,7 +36562,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="861" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F861" s="1" t="s">
         <v>226</v>
       </c>
@@ -36570,7 +36582,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="862" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F862" s="1" t="s">
         <v>87</v>
       </c>
@@ -36590,7 +36602,7 @@
         <v>444.99999999999994</v>
       </c>
     </row>
-    <row r="863" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A863" s="1" t="s">
         <v>19</v>
       </c>
@@ -36628,7 +36640,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="864" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A864" s="1" t="s">
         <v>19</v>
       </c>
@@ -36666,7 +36678,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="865" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A865" s="1" t="s">
         <v>19</v>
       </c>
@@ -36704,7 +36716,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="866" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A866" s="1" t="s">
         <v>19</v>
       </c>
@@ -36742,7 +36754,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="867" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A867" s="1" t="s">
         <v>19</v>
       </c>
@@ -36780,7 +36792,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="868" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A868" s="1" t="s">
         <v>19</v>
       </c>
@@ -36818,7 +36830,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="869" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A869" s="1" t="s">
         <v>19</v>
       </c>
@@ -36856,7 +36868,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="870" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A870" s="1" t="s">
         <v>19</v>
       </c>
@@ -36894,7 +36906,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="871" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A871" s="1" t="s">
         <v>19</v>
       </c>
@@ -36932,7 +36944,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="872" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A872" s="1" t="s">
         <v>19</v>
       </c>
@@ -36970,7 +36982,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="873" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A873" s="1" t="s">
         <v>19</v>
       </c>
@@ -37008,7 +37020,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="874" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A874" s="1" t="s">
         <v>19</v>
       </c>
@@ -37046,7 +37058,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="875" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A875" s="1" t="s">
         <v>19</v>
       </c>
@@ -37084,7 +37096,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="876" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A876" s="1" t="s">
         <v>19</v>
       </c>
@@ -37122,7 +37134,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="877" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A877" s="1" t="s">
         <v>19</v>
       </c>
@@ -37160,7 +37172,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="878" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A878" s="1" t="s">
         <v>19</v>
       </c>
@@ -37198,7 +37210,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="879" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A879" s="1" t="s">
         <v>19</v>
       </c>
@@ -37236,7 +37248,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="880" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A880" s="1" t="s">
         <v>19</v>
       </c>
@@ -37274,7 +37286,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="881" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A881" s="1" t="s">
         <v>19</v>
       </c>
@@ -37312,7 +37324,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="882" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A882" s="1" t="s">
         <v>19</v>
       </c>
@@ -37350,7 +37362,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="883" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A883" s="1" t="s">
         <v>19</v>
       </c>
@@ -37388,7 +37400,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="884" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A884" s="1" t="s">
         <v>19</v>
       </c>
@@ -37426,7 +37438,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="885" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A885" s="1" t="s">
         <v>19</v>
       </c>
@@ -37464,7 +37476,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="886" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A886" s="1" t="s">
         <v>19</v>
       </c>
@@ -37502,7 +37514,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="887" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A887" s="1" t="s">
         <v>19</v>
       </c>
@@ -37540,7 +37552,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="888" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A888" s="1" t="s">
         <v>19</v>
       </c>
@@ -37578,7 +37590,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="889" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A889" s="1" t="s">
         <v>19</v>
       </c>
@@ -37616,7 +37628,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="890" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A890" s="1" t="s">
         <v>19</v>
       </c>
@@ -37654,7 +37666,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="891" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A891" s="1" t="s">
         <v>19</v>
       </c>
@@ -37692,7 +37704,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="892" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A892" s="1" t="s">
         <v>19</v>
       </c>
@@ -37730,7 +37742,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="893" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A893" s="1" t="s">
         <v>19</v>
       </c>
@@ -37768,7 +37780,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="894" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A894" s="1" t="s">
         <v>19</v>
       </c>
@@ -37806,7 +37818,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="895" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A895" s="1" t="s">
         <v>19</v>
       </c>
@@ -37844,7 +37856,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="896" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A896" s="1" t="s">
         <v>19</v>
       </c>
@@ -37882,7 +37894,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="897" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A897" s="1" t="s">
         <v>19</v>
       </c>
@@ -37920,7 +37932,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="898" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A898" s="1" t="s">
         <v>19</v>
       </c>
@@ -37958,7 +37970,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="899" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A899" s="1" t="s">
         <v>19</v>
       </c>
@@ -37996,7 +38008,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="900" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A900" s="1" t="s">
         <v>19</v>
       </c>
@@ -38034,7 +38046,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="901" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A901" s="1" t="s">
         <v>19</v>
       </c>
@@ -38072,7 +38084,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="902" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A902" s="1" t="s">
         <v>19</v>
       </c>
@@ -38110,7 +38122,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="903" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A903" s="1" t="s">
         <v>19</v>
       </c>
@@ -38148,7 +38160,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="904" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A904" s="1" t="s">
         <v>19</v>
       </c>
@@ -38186,7 +38198,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="905" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A905" s="1" t="s">
         <v>19</v>
       </c>
@@ -38224,7 +38236,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="906" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A906" s="1" t="s">
         <v>19</v>
       </c>
@@ -38262,7 +38274,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="907" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F907" s="1" t="s">
         <v>226</v>
       </c>
@@ -38282,7 +38294,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="908" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F908" s="1" t="s">
         <v>1147</v>
       </c>
@@ -38302,7 +38314,7 @@
         <v>932.8</v>
       </c>
     </row>
-    <row r="909" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A909" s="1" t="s">
         <v>19</v>
       </c>
@@ -38340,7 +38352,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="910" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A910" s="1" t="s">
         <v>19</v>
       </c>
@@ -38378,7 +38390,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="911" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A911" s="1" t="s">
         <v>19</v>
       </c>
@@ -38416,7 +38428,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="912" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A912" s="1" t="s">
         <v>19</v>
       </c>
@@ -38454,7 +38466,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="913" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A913" s="1" t="s">
         <v>19</v>
       </c>
@@ -38492,7 +38504,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="914" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A914" s="1" t="s">
         <v>19</v>
       </c>
@@ -38530,7 +38542,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="915" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A915" s="1" t="s">
         <v>19</v>
       </c>
@@ -38568,7 +38580,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="916" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A916" s="1" t="s">
         <v>19</v>
       </c>
@@ -38606,7 +38618,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="917" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A917" s="1" t="s">
         <v>19</v>
       </c>
@@ -38644,7 +38656,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="918" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A918" s="1" t="s">
         <v>19</v>
       </c>
@@ -38682,7 +38694,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="919" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A919" s="1" t="s">
         <v>19</v>
       </c>
@@ -38720,7 +38732,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="920" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A920" s="1" t="s">
         <v>19</v>
       </c>
@@ -38758,7 +38770,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="921" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A921" s="1" t="s">
         <v>19</v>
       </c>
@@ -38796,7 +38808,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="922" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A922" s="1" t="s">
         <v>19</v>
       </c>
@@ -38834,7 +38846,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="923" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A923" s="1" t="s">
         <v>19</v>
       </c>
@@ -38872,7 +38884,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="924" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A924" s="1" t="s">
         <v>19</v>
       </c>
@@ -38910,7 +38922,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="925" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A925" s="1" t="s">
         <v>19</v>
       </c>
@@ -38948,7 +38960,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="926" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A926" s="1" t="s">
         <v>19</v>
       </c>
@@ -38986,7 +38998,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="927" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A927" s="1" t="s">
         <v>19</v>
       </c>
@@ -39024,7 +39036,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="928" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A928" s="1" t="s">
         <v>19</v>
       </c>
@@ -39062,7 +39074,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="929" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F929" s="1" t="s">
         <v>226</v>
       </c>
@@ -39082,7 +39094,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="930" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F930" s="1" t="s">
         <v>83</v>
       </c>
@@ -39102,7 +39114,7 @@
         <v>417.59999999999991</v>
       </c>
     </row>
-    <row r="931" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A931" s="1" t="s">
         <v>19</v>
       </c>
@@ -39140,7 +39152,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="932" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A932" s="1" t="s">
         <v>19</v>
       </c>
@@ -39178,7 +39190,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="933" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A933" s="1" t="s">
         <v>19</v>
       </c>
@@ -39216,7 +39228,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="934" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A934" s="1" t="s">
         <v>19</v>
       </c>
@@ -39254,7 +39266,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="935" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A935" s="1" t="s">
         <v>19</v>
       </c>
@@ -39292,7 +39304,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="936" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A936" s="1" t="s">
         <v>19</v>
       </c>
@@ -39330,7 +39342,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="937" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A937" s="1" t="s">
         <v>19</v>
       </c>
@@ -39368,7 +39380,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="938" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A938" s="1" t="s">
         <v>19</v>
       </c>
@@ -39406,7 +39418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="939" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A939" s="1" t="s">
         <v>19</v>
       </c>
@@ -39444,7 +39456,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="940" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A940" s="1" t="s">
         <v>19</v>
       </c>
@@ -39482,7 +39494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="941" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A941" s="1" t="s">
         <v>19</v>
       </c>
@@ -39520,7 +39532,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="942" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A942" s="1" t="s">
         <v>19</v>
       </c>
@@ -39558,7 +39570,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="943" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A943" s="1" t="s">
         <v>19</v>
       </c>
@@ -39596,7 +39608,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="944" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A944" s="1" t="s">
         <v>19</v>
       </c>
@@ -39634,7 +39646,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="945" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A945" s="1" t="s">
         <v>19</v>
       </c>
@@ -39672,7 +39684,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="946" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A946" s="1" t="s">
         <v>19</v>
       </c>
@@ -39710,7 +39722,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="947" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A947" s="1" t="s">
         <v>19</v>
       </c>
@@ -39748,7 +39760,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="948" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A948" s="1" t="s">
         <v>19</v>
       </c>
@@ -39786,7 +39798,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="949" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A949" s="1" t="s">
         <v>19</v>
       </c>
@@ -39824,7 +39836,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="950" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A950" s="1" t="s">
         <v>19</v>
       </c>
@@ -39862,7 +39874,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="951" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A951" s="1" t="s">
         <v>19</v>
       </c>
@@ -39900,7 +39912,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="952" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A952" s="1" t="s">
         <v>19</v>
       </c>
@@ -39938,7 +39950,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="953" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F953" s="1" t="s">
         <v>226</v>
       </c>
@@ -39958,7 +39970,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="954" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F954" s="1" t="s">
         <v>87</v>
       </c>
@@ -39975,7 +39987,7 @@
         <v>456.40000000000003</v>
       </c>
     </row>
-    <row r="955" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A955" s="1" t="s">
         <v>19</v>
       </c>
@@ -40013,7 +40025,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="956" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A956" s="1" t="s">
         <v>19</v>
       </c>
@@ -40051,7 +40063,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="957" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A957" s="1" t="s">
         <v>19</v>
       </c>
@@ -40089,7 +40101,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="958" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A958" s="1" t="s">
         <v>19</v>
       </c>
@@ -40127,7 +40139,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="959" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A959" s="1" t="s">
         <v>19</v>
       </c>
@@ -40165,7 +40177,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="960" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A960" s="1" t="s">
         <v>19</v>
       </c>
@@ -40203,7 +40215,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="961" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A961" s="1" t="s">
         <v>19</v>
       </c>
@@ -40241,7 +40253,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="962" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A962" s="1" t="s">
         <v>19</v>
       </c>
@@ -40279,7 +40291,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="963" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A963" s="1" t="s">
         <v>19</v>
       </c>
@@ -40317,7 +40329,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="964" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A964" s="1" t="s">
         <v>19</v>
       </c>
@@ -40355,7 +40367,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="965" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A965" s="1" t="s">
         <v>19</v>
       </c>
@@ -40393,7 +40405,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="966" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A966" s="1" t="s">
         <v>19</v>
       </c>
@@ -40431,7 +40443,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="967" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A967" s="1" t="s">
         <v>19</v>
       </c>
@@ -40469,7 +40481,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="968" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A968" s="1" t="s">
         <v>19</v>
       </c>
@@ -40507,7 +40519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="969" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A969" s="1" t="s">
         <v>19</v>
       </c>
@@ -40545,7 +40557,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="970" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A970" s="1" t="s">
         <v>19</v>
       </c>
@@ -40583,7 +40595,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="971" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A971" s="1" t="s">
         <v>19</v>
       </c>
@@ -40621,7 +40633,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="972" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A972" s="1" t="s">
         <v>19</v>
       </c>
@@ -40659,7 +40671,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="973" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A973" s="1" t="s">
         <v>19</v>
       </c>
@@ -40697,7 +40709,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="974" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A974" s="1" t="s">
         <v>19</v>
       </c>
@@ -40735,7 +40747,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="975" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A975" s="1" t="s">
         <v>19</v>
       </c>
@@ -40773,7 +40785,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="976" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A976" s="1" t="s">
         <v>19</v>
       </c>
@@ -40811,7 +40823,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="977" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F977" s="1" t="s">
         <v>226</v>
       </c>
@@ -40831,7 +40843,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="978" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F978" s="1" t="s">
         <v>87</v>
       </c>
@@ -40854,7 +40866,7 @@
         <v>450.79999999999995</v>
       </c>
     </row>
-    <row r="979" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A979" s="1" t="s">
         <v>19</v>
       </c>
@@ -40892,7 +40904,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="980" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A980" s="1" t="s">
         <v>19</v>
       </c>
@@ -40930,7 +40942,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="981" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A981" s="1" t="s">
         <v>19</v>
       </c>
@@ -40968,7 +40980,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="982" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A982" s="1" t="s">
         <v>19</v>
       </c>
@@ -41006,7 +41018,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="983" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A983" s="1" t="s">
         <v>19</v>
       </c>
@@ -41044,7 +41056,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="984" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A984" s="1" t="s">
         <v>19</v>
       </c>
@@ -41082,7 +41094,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="985" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A985" s="1" t="s">
         <v>19</v>
       </c>
@@ -41120,7 +41132,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="986" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A986" s="1" t="s">
         <v>19</v>
       </c>
@@ -41158,7 +41170,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="987" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A987" s="1" t="s">
         <v>19</v>
       </c>
@@ -41196,7 +41208,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="988" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A988" s="1" t="s">
         <v>19</v>
       </c>
@@ -41234,7 +41246,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="989" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A989" s="1" t="s">
         <v>19</v>
       </c>
@@ -41272,7 +41284,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="990" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A990" s="1" t="s">
         <v>19</v>
       </c>
@@ -41310,7 +41322,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="991" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A991" s="1" t="s">
         <v>19</v>
       </c>
@@ -41348,7 +41360,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="992" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A992" s="1" t="s">
         <v>19</v>
       </c>
@@ -41386,7 +41398,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="993" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A993" s="1" t="s">
         <v>19</v>
       </c>
@@ -41424,7 +41436,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="994" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A994" s="1" t="s">
         <v>19</v>
       </c>
@@ -41462,7 +41474,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="995" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A995" s="1" t="s">
         <v>19</v>
       </c>
@@ -41500,7 +41512,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="996" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A996" s="1" t="s">
         <v>19</v>
       </c>
@@ -41538,7 +41550,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="997" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A997" s="1" t="s">
         <v>19</v>
       </c>
@@ -41576,7 +41588,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="998" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A998" s="1" t="s">
         <v>19</v>
       </c>
@@ -41614,7 +41626,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="999" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A999" s="1" t="s">
         <v>19</v>
       </c>
@@ -41652,7 +41664,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="1000" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1000" s="1" t="s">
         <v>19</v>
       </c>
@@ -41690,7 +41702,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="1001" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1001" s="1" t="s">
         <v>19</v>
       </c>
@@ -41728,7 +41740,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="1002" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1002" s="1" t="s">
         <v>19</v>
       </c>
@@ -41766,7 +41778,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="1003" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1003" s="1" t="s">
         <v>19</v>
       </c>
@@ -41804,7 +41816,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="1004" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1004" s="1" t="s">
         <v>19</v>
       </c>
@@ -41842,7 +41854,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="1005" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1005" s="1" t="s">
         <v>19</v>
       </c>
@@ -41880,7 +41892,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="1006" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1006" s="1" t="s">
         <v>19</v>
       </c>
@@ -41918,7 +41930,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="1007" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1007" s="1" t="s">
         <v>19</v>
       </c>
@@ -41956,7 +41968,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="1008" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1008" s="1" t="s">
         <v>19</v>
       </c>
@@ -41994,7 +42006,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="1009" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1009" s="1" t="s">
         <v>19</v>
       </c>
@@ -42032,7 +42044,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="1010" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1010" s="1" t="s">
         <v>19</v>
       </c>
@@ -42070,7 +42082,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="1011" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1011" s="1" t="s">
         <v>19</v>
       </c>
@@ -42108,7 +42120,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="1012" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1012" s="1" t="s">
         <v>19</v>
       </c>
@@ -42146,7 +42158,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="1013" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1013" s="1" t="s">
         <v>19</v>
       </c>
@@ -42184,7 +42196,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="1014" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1014" s="1" t="s">
         <v>19</v>
       </c>
@@ -42222,7 +42234,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="1015" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1015" s="1" t="s">
         <v>19</v>
       </c>
@@ -42260,7 +42272,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="1016" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1016" s="1" t="s">
         <v>19</v>
       </c>
@@ -42298,7 +42310,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="1017" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1017" s="1" t="s">
         <v>19</v>
       </c>
@@ -42336,7 +42348,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="1018" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1018" s="1" t="s">
         <v>19</v>
       </c>
@@ -42374,7 +42386,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="1019" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1019" s="1" t="s">
         <v>19</v>
       </c>
@@ -42412,7 +42424,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="1020" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1020" s="1" t="s">
         <v>19</v>
       </c>
@@ -42450,7 +42462,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="1021" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1021" s="1" t="s">
         <v>19</v>
       </c>
@@ -42488,7 +42500,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="1022" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1022" s="1" t="s">
         <v>19</v>
       </c>
@@ -42526,7 +42538,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="1023" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1023" s="1" t="s">
         <v>19</v>
       </c>
@@ -42564,7 +42576,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="1024" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1024" s="1" t="s">
         <v>19</v>
       </c>
@@ -42602,7 +42614,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="1025" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1025" s="1" t="s">
         <v>19</v>
       </c>
@@ -42640,7 +42652,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="1026" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1026" s="1" t="s">
         <v>19</v>
       </c>
@@ -42678,7 +42690,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="1027" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1027" s="1" t="s">
         <v>19</v>
       </c>
@@ -42716,7 +42728,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="1028" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1028" s="1" t="s">
         <v>19</v>
       </c>
@@ -42754,7 +42766,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="1029" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1029" s="1" t="s">
         <v>19</v>
       </c>
@@ -42792,7 +42804,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="1030" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1030" s="1" t="s">
         <v>19</v>
       </c>
@@ -42830,7 +42842,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="1031" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1031" s="1" t="s">
         <v>19</v>
       </c>
@@ -42868,7 +42880,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="1032" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1032" s="1" t="s">
         <v>19</v>
       </c>
@@ -42906,7 +42918,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="1033" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1033" s="1" t="s">
         <v>19</v>
       </c>
@@ -42944,7 +42956,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="1034" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1034" s="1" t="s">
         <v>19</v>
       </c>
@@ -42982,7 +42994,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="1035" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1035" s="1" t="s">
         <v>19</v>
       </c>
@@ -43020,7 +43032,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="1036" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1036" s="1" t="s">
         <v>19</v>
       </c>
@@ -43058,7 +43070,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="1037" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1037" s="1" t="s">
         <v>19</v>
       </c>
@@ -43096,7 +43108,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="1038" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1038" s="1" t="s">
         <v>19</v>
       </c>
@@ -43134,7 +43146,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="1039" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1039" s="1" t="s">
         <v>19</v>
       </c>
@@ -43172,7 +43184,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="1040" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1040" s="1" t="s">
         <v>19</v>
       </c>
@@ -43210,7 +43222,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="1041" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1041" s="1" t="s">
         <v>19</v>
       </c>
@@ -43248,7 +43260,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="1042" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1042" s="1" t="s">
         <v>19</v>
       </c>
@@ -43286,7 +43298,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="1043" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1043" s="1" t="s">
         <v>19</v>
       </c>
@@ -43324,7 +43336,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="1044" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1044" s="1" t="s">
         <v>19</v>
       </c>
@@ -43362,7 +43374,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="1045" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1045" s="1" t="s">
         <v>226</v>
       </c>
@@ -43382,7 +43394,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="1046" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1046" s="1" t="s">
         <v>1290</v>
       </c>
@@ -43402,7 +43414,7 @@
         <v>1403.5</v>
       </c>
     </row>
-    <row r="1047" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1047" s="1" t="s">
         <v>226</v>
       </c>
@@ -43422,7 +43434,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="1049" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1049" s="1" t="s">
         <v>1291</v>
       </c>
@@ -43460,7 +43472,7 @@
         <v>104.3</v>
       </c>
     </row>
-    <row r="1050" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1050" s="1" t="s">
         <v>226</v>
       </c>
@@ -43480,7 +43492,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="1052" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1052" s="1" t="s">
         <v>1291</v>
       </c>
@@ -43518,7 +43530,7 @@
         <v>194.8</v>
       </c>
     </row>
-    <row r="1053" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1053" s="1" t="s">
         <v>226</v>
       </c>
@@ -43538,7 +43550,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="1055" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1055" s="1" t="s">
         <v>1291</v>
       </c>
@@ -43576,7 +43588,7 @@
         <v>109.8</v>
       </c>
     </row>
-    <row r="1056" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1056" s="1" t="s">
         <v>226</v>
       </c>
@@ -43596,7 +43608,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="1058" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1058" s="1" t="s">
         <v>1291</v>
       </c>
@@ -43634,7 +43646,7 @@
         <v>52.8</v>
       </c>
     </row>
-    <row r="1059" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1059" s="1" t="s">
         <v>226</v>
       </c>
@@ -43654,12 +43666,12 @@
         <v>227</v>
       </c>
     </row>
-    <row r="1060" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K1060" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="1061" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1061" s="1" t="s">
         <v>1291</v>
       </c>
@@ -43697,7 +43709,7 @@
         <v>162.80000000000001</v>
       </c>
     </row>
-    <row r="1062" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1062" s="1" t="s">
         <v>226</v>
       </c>
@@ -43717,12 +43729,12 @@
         <v>227</v>
       </c>
     </row>
-    <row r="1063" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K1063" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="1064" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1064" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1064" s="1" t="s">
         <v>1291</v>
       </c>
@@ -43760,7 +43772,7 @@
         <v>108.4</v>
       </c>
     </row>
-    <row r="1065" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1065" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1065" s="1" t="s">
         <v>226</v>
       </c>
@@ -43780,12 +43792,12 @@
         <v>227</v>
       </c>
     </row>
-    <row r="1066" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1066" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K1066" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="1067" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1067" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1067" s="1" t="s">
         <v>1291</v>
       </c>
@@ -43823,7 +43835,7 @@
         <v>309.5</v>
       </c>
     </row>
-    <row r="1068" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1068" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1068" s="1" t="s">
         <v>226</v>
       </c>
@@ -43843,7 +43855,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="1070" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1070" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1070" s="1" t="s">
         <v>1291</v>
       </c>
@@ -43881,7 +43893,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="1071" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1071" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1071" s="1" t="s">
         <v>226</v>
       </c>
@@ -43901,12 +43913,12 @@
         <v>227</v>
       </c>
     </row>
-    <row r="1072" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1072" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K1072" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="1073" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1073" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1073" s="1" t="s">
         <v>1291</v>
       </c>
@@ -43944,7 +43956,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="1074" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1074" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1074" s="1" t="s">
         <v>226</v>
       </c>
@@ -43964,12 +43976,12 @@
         <v>227</v>
       </c>
     </row>
-    <row r="1075" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1075" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K1075" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="1076" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1076" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1076" s="1" t="s">
         <v>1291</v>
       </c>
@@ -44007,7 +44019,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="1077" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1077" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1077" s="1" t="s">
         <v>226</v>
       </c>
@@ -44027,12 +44039,12 @@
         <v>227</v>
       </c>
     </row>
-    <row r="1078" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1078" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J1078" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="1079" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1079" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1079" s="1" t="s">
         <v>1291</v>
       </c>
@@ -44070,7 +44082,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="1080" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1080" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1080" s="1" t="s">
         <v>226</v>
       </c>
@@ -44090,7 +44102,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="1082" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1082" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1082" s="1" t="s">
         <v>1291</v>
       </c>
@@ -44128,7 +44140,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="1083" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1083" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1083" s="1" t="s">
         <v>226</v>
       </c>
@@ -44148,12 +44160,12 @@
         <v>227</v>
       </c>
     </row>
-    <row r="1084" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1084" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K1084" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="1085" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1085" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1085" s="1" t="s">
         <v>1291</v>
       </c>
@@ -44191,7 +44203,7 @@
         <v>81.599999999999994</v>
       </c>
     </row>
-    <row r="1086" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1086" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F1086" s="1" t="s">
         <v>226</v>
       </c>
@@ -44215,4 +44227,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B2CCB1A-958A-4C3D-8894-2608604A6FB8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>47555</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>